--- a/data/seat/02-febrero2026.xlsx
+++ b/data/seat/02-febrero2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Filezilla/2021/Energia/2026/Febrero/28-02-2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Datos/Energía/SEAT/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{35F57E0A-C92F-4218-AA83-EBB438455458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81496967-C2E3-4BBB-83F1-F61D7DC460CC}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{35F57E0A-C92F-4218-AA83-EBB438455458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD936F0D-0B0B-49E9-B02D-C55882F64F3F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEAT-SERs" sheetId="1" r:id="rId1"/>
@@ -2016,60 +2016,6 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2100,6 +2046,39 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2112,10 +2091,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3401,40 +3401,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>23410</c:v>
+                  <c:v>22712</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38647</c:v>
+                  <c:v>37949</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>39214</c:v>
+                  <c:v>38516</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>40919</c:v>
+                  <c:v>40221</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>39560</c:v>
+                  <c:v>38862</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>39407</c:v>
+                  <c:v>38709</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>28130</c:v>
+                  <c:v>27432</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21214</c:v>
+                  <c:v>20516</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38830</c:v>
+                  <c:v>38132</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>38469</c:v>
+                  <c:v>37771</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>38750</c:v>
+                  <c:v>38052</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>39845.440000000002</c:v>
+                  <c:v>39147.440000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3691,40 +3691,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>5440</c:v>
+                  <c:v>6138</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6673</c:v>
+                  <c:v>7371</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6844</c:v>
+                  <c:v>7542</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6985</c:v>
+                  <c:v>7683</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7160</c:v>
+                  <c:v>7858</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7145</c:v>
+                  <c:v>7843</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5820</c:v>
+                  <c:v>6518</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5796</c:v>
+                  <c:v>6494</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6710</c:v>
+                  <c:v>7408</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7023</c:v>
+                  <c:v>7721</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7050</c:v>
+                  <c:v>7748</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7042.5599999999995</c:v>
+                  <c:v>7740.5599999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6922,7 +6922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BS41"/>
+  <dimension ref="A1:BU41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" style="134" customWidth="1"/>
@@ -6975,301 +6975,301 @@
     <col min="70" max="70" width="9.28515625" style="14" customWidth="1"/>
     <col min="71" max="71" width="2.7109375" style="14" customWidth="1"/>
     <col min="72" max="72" width="6.85546875" style="14" customWidth="1"/>
-    <col min="73" max="73" width="6.42578125" style="14" customWidth="1"/>
+    <col min="73" max="73" width="12.140625" style="14" customWidth="1"/>
     <col min="74" max="16384" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" s="133" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:73" s="133" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="127">
         <v>1.1111111E+55</v>
       </c>
-      <c r="B1" s="202" t="s">
+      <c r="B1" s="184" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="128"/>
-      <c r="D1" s="204" t="s">
+      <c r="D1" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="205"/>
-      <c r="F1" s="205"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="205"/>
-      <c r="L1" s="205"/>
-      <c r="M1" s="205"/>
-      <c r="N1" s="205"/>
-      <c r="O1" s="206"/>
-      <c r="P1" s="207"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
+      <c r="L1" s="187"/>
+      <c r="M1" s="187"/>
+      <c r="N1" s="187"/>
+      <c r="O1" s="188"/>
+      <c r="P1" s="189"/>
       <c r="Q1" s="129"/>
-      <c r="R1" s="184" t="s">
+      <c r="R1" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="185"/>
-      <c r="T1" s="185"/>
-      <c r="U1" s="185"/>
-      <c r="V1" s="185"/>
-      <c r="W1" s="185"/>
-      <c r="X1" s="185"/>
-      <c r="Y1" s="185"/>
-      <c r="Z1" s="185"/>
-      <c r="AA1" s="186"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
+      <c r="V1" s="195"/>
+      <c r="W1" s="195"/>
+      <c r="X1" s="195"/>
+      <c r="Y1" s="195"/>
+      <c r="Z1" s="195"/>
+      <c r="AA1" s="196"/>
       <c r="AB1" s="130"/>
-      <c r="AC1" s="184" t="s">
+      <c r="AC1" s="194" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="185"/>
-      <c r="AE1" s="185"/>
-      <c r="AF1" s="185"/>
-      <c r="AG1" s="185"/>
-      <c r="AH1" s="185"/>
-      <c r="AI1" s="185"/>
-      <c r="AJ1" s="185"/>
-      <c r="AK1" s="186"/>
+      <c r="AD1" s="195"/>
+      <c r="AE1" s="195"/>
+      <c r="AF1" s="195"/>
+      <c r="AG1" s="195"/>
+      <c r="AH1" s="195"/>
+      <c r="AI1" s="195"/>
+      <c r="AJ1" s="195"/>
+      <c r="AK1" s="196"/>
       <c r="AL1" s="131"/>
-      <c r="AM1" s="184" t="s">
+      <c r="AM1" s="194" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="185"/>
-      <c r="AO1" s="185"/>
-      <c r="AP1" s="185"/>
-      <c r="AQ1" s="185"/>
-      <c r="AR1" s="185"/>
-      <c r="AS1" s="185"/>
-      <c r="AT1" s="185"/>
-      <c r="AU1" s="186"/>
+      <c r="AN1" s="195"/>
+      <c r="AO1" s="195"/>
+      <c r="AP1" s="195"/>
+      <c r="AQ1" s="195"/>
+      <c r="AR1" s="195"/>
+      <c r="AS1" s="195"/>
+      <c r="AT1" s="195"/>
+      <c r="AU1" s="196"/>
       <c r="AV1" s="131"/>
-      <c r="AW1" s="184" t="s">
+      <c r="AW1" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="185"/>
-      <c r="AY1" s="185"/>
-      <c r="AZ1" s="185"/>
-      <c r="BA1" s="185"/>
-      <c r="BB1" s="185"/>
-      <c r="BC1" s="185"/>
-      <c r="BD1" s="185"/>
-      <c r="BE1" s="185"/>
-      <c r="BF1" s="185"/>
-      <c r="BG1" s="185"/>
-      <c r="BH1" s="186"/>
+      <c r="AX1" s="195"/>
+      <c r="AY1" s="195"/>
+      <c r="AZ1" s="195"/>
+      <c r="BA1" s="195"/>
+      <c r="BB1" s="195"/>
+      <c r="BC1" s="195"/>
+      <c r="BD1" s="195"/>
+      <c r="BE1" s="195"/>
+      <c r="BF1" s="195"/>
+      <c r="BG1" s="195"/>
+      <c r="BH1" s="196"/>
       <c r="BI1" s="131"/>
-      <c r="BJ1" s="184" t="s">
+      <c r="BJ1" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="BK1" s="185"/>
-      <c r="BL1" s="185"/>
-      <c r="BM1" s="185"/>
-      <c r="BN1" s="185"/>
-      <c r="BO1" s="185"/>
-      <c r="BP1" s="185"/>
-      <c r="BQ1" s="185"/>
-      <c r="BR1" s="186"/>
+      <c r="BK1" s="195"/>
+      <c r="BL1" s="195"/>
+      <c r="BM1" s="195"/>
+      <c r="BN1" s="195"/>
+      <c r="BO1" s="195"/>
+      <c r="BP1" s="195"/>
+      <c r="BQ1" s="195"/>
+      <c r="BR1" s="196"/>
       <c r="BS1" s="132"/>
     </row>
-    <row r="2" spans="1:71" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="202"/>
+    <row r="2" spans="1:73" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="184"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="209"/>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
-      <c r="M2" s="209"/>
-      <c r="N2" s="209"/>
-      <c r="O2" s="210"/>
-      <c r="P2" s="211"/>
+      <c r="D2" s="190"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
+      <c r="K2" s="191"/>
+      <c r="L2" s="191"/>
+      <c r="M2" s="191"/>
+      <c r="N2" s="191"/>
+      <c r="O2" s="192"/>
+      <c r="P2" s="193"/>
       <c r="Q2" s="58"/>
-      <c r="R2" s="187"/>
-      <c r="S2" s="188"/>
-      <c r="T2" s="188"/>
-      <c r="U2" s="188"/>
-      <c r="V2" s="188"/>
-      <c r="W2" s="188"/>
-      <c r="X2" s="188"/>
-      <c r="Y2" s="188"/>
-      <c r="Z2" s="188"/>
-      <c r="AA2" s="189"/>
+      <c r="R2" s="197"/>
+      <c r="S2" s="198"/>
+      <c r="T2" s="198"/>
+      <c r="U2" s="198"/>
+      <c r="V2" s="198"/>
+      <c r="W2" s="198"/>
+      <c r="X2" s="198"/>
+      <c r="Y2" s="198"/>
+      <c r="Z2" s="198"/>
+      <c r="AA2" s="199"/>
       <c r="AB2" s="60"/>
-      <c r="AC2" s="187"/>
-      <c r="AD2" s="188"/>
-      <c r="AE2" s="188"/>
-      <c r="AF2" s="188"/>
-      <c r="AG2" s="188"/>
-      <c r="AH2" s="188"/>
-      <c r="AI2" s="188"/>
-      <c r="AJ2" s="188"/>
-      <c r="AK2" s="189"/>
+      <c r="AC2" s="197"/>
+      <c r="AD2" s="198"/>
+      <c r="AE2" s="198"/>
+      <c r="AF2" s="198"/>
+      <c r="AG2" s="198"/>
+      <c r="AH2" s="198"/>
+      <c r="AI2" s="198"/>
+      <c r="AJ2" s="198"/>
+      <c r="AK2" s="199"/>
       <c r="AL2" s="59"/>
-      <c r="AM2" s="187"/>
-      <c r="AN2" s="188"/>
-      <c r="AO2" s="188"/>
-      <c r="AP2" s="188"/>
-      <c r="AQ2" s="188"/>
-      <c r="AR2" s="188"/>
-      <c r="AS2" s="188"/>
-      <c r="AT2" s="188"/>
-      <c r="AU2" s="189"/>
+      <c r="AM2" s="197"/>
+      <c r="AN2" s="198"/>
+      <c r="AO2" s="198"/>
+      <c r="AP2" s="198"/>
+      <c r="AQ2" s="198"/>
+      <c r="AR2" s="198"/>
+      <c r="AS2" s="198"/>
+      <c r="AT2" s="198"/>
+      <c r="AU2" s="199"/>
       <c r="AV2" s="59"/>
-      <c r="AW2" s="187"/>
-      <c r="AX2" s="188"/>
-      <c r="AY2" s="188"/>
-      <c r="AZ2" s="188"/>
-      <c r="BA2" s="188"/>
-      <c r="BB2" s="188"/>
-      <c r="BC2" s="188"/>
-      <c r="BD2" s="188"/>
-      <c r="BE2" s="188"/>
-      <c r="BF2" s="188"/>
-      <c r="BG2" s="188"/>
-      <c r="BH2" s="189"/>
+      <c r="AW2" s="197"/>
+      <c r="AX2" s="198"/>
+      <c r="AY2" s="198"/>
+      <c r="AZ2" s="198"/>
+      <c r="BA2" s="198"/>
+      <c r="BB2" s="198"/>
+      <c r="BC2" s="198"/>
+      <c r="BD2" s="198"/>
+      <c r="BE2" s="198"/>
+      <c r="BF2" s="198"/>
+      <c r="BG2" s="198"/>
+      <c r="BH2" s="199"/>
       <c r="BI2" s="59"/>
-      <c r="BJ2" s="187"/>
-      <c r="BK2" s="188"/>
-      <c r="BL2" s="188"/>
-      <c r="BM2" s="188"/>
-      <c r="BN2" s="188"/>
-      <c r="BO2" s="188"/>
-      <c r="BP2" s="188"/>
-      <c r="BQ2" s="188"/>
-      <c r="BR2" s="189"/>
+      <c r="BJ2" s="197"/>
+      <c r="BK2" s="198"/>
+      <c r="BL2" s="198"/>
+      <c r="BM2" s="198"/>
+      <c r="BN2" s="198"/>
+      <c r="BO2" s="198"/>
+      <c r="BP2" s="198"/>
+      <c r="BQ2" s="198"/>
+      <c r="BR2" s="199"/>
       <c r="BS2" s="135"/>
     </row>
-    <row r="3" spans="1:71" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="202"/>
+    <row r="3" spans="1:73" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="184"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="190" t="s">
+      <c r="D3" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="190" t="s">
+      <c r="E3" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="190" t="s">
+      <c r="F3" s="203" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="190" t="s">
+      <c r="G3" s="203" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="190" t="s">
+      <c r="H3" s="203" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="212" t="s">
+      <c r="I3" s="205" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="213"/>
-      <c r="K3" s="214"/>
-      <c r="L3" s="215"/>
-      <c r="M3" s="212" t="s">
+      <c r="J3" s="206"/>
+      <c r="K3" s="207"/>
+      <c r="L3" s="208"/>
+      <c r="M3" s="205" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="213"/>
-      <c r="O3" s="214"/>
-      <c r="P3" s="215"/>
+      <c r="N3" s="206"/>
+      <c r="O3" s="207"/>
+      <c r="P3" s="208"/>
       <c r="Q3" s="58"/>
-      <c r="R3" s="194" t="s">
+      <c r="R3" s="209" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="195"/>
-      <c r="T3" s="216"/>
-      <c r="U3" s="216"/>
-      <c r="V3" s="194" t="s">
+      <c r="S3" s="201"/>
+      <c r="T3" s="210"/>
+      <c r="U3" s="210"/>
+      <c r="V3" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="195"/>
-      <c r="X3" s="195"/>
-      <c r="Y3" s="195"/>
-      <c r="Z3" s="195"/>
-      <c r="AA3" s="196"/>
+      <c r="W3" s="201"/>
+      <c r="X3" s="201"/>
+      <c r="Y3" s="201"/>
+      <c r="Z3" s="201"/>
+      <c r="AA3" s="202"/>
       <c r="AB3" s="60"/>
-      <c r="AC3" s="192" t="s">
+      <c r="AC3" s="211" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="217" t="s">
+      <c r="AD3" s="213" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="194" t="s">
+      <c r="AE3" s="209" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="195"/>
-      <c r="AG3" s="196"/>
-      <c r="AH3" s="194" t="s">
+      <c r="AF3" s="201"/>
+      <c r="AG3" s="202"/>
+      <c r="AH3" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="195"/>
-      <c r="AJ3" s="195"/>
-      <c r="AK3" s="196"/>
+      <c r="AI3" s="201"/>
+      <c r="AJ3" s="201"/>
+      <c r="AK3" s="202"/>
       <c r="AL3" s="59"/>
-      <c r="AM3" s="197" t="s">
+      <c r="AM3" s="214" t="s">
         <v>15</v>
       </c>
-      <c r="AN3" s="192" t="s">
+      <c r="AN3" s="211" t="s">
         <v>9</v>
       </c>
-      <c r="AO3" s="201" t="s">
+      <c r="AO3" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="195"/>
-      <c r="AQ3" s="196"/>
-      <c r="AR3" s="194" t="s">
+      <c r="AP3" s="201"/>
+      <c r="AQ3" s="202"/>
+      <c r="AR3" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="AS3" s="195"/>
-      <c r="AT3" s="195"/>
-      <c r="AU3" s="196"/>
+      <c r="AS3" s="201"/>
+      <c r="AT3" s="201"/>
+      <c r="AU3" s="202"/>
       <c r="AV3" s="59"/>
-      <c r="AW3" s="192" t="s">
+      <c r="AW3" s="211" t="s">
         <v>15</v>
       </c>
-      <c r="AX3" s="192" t="s">
+      <c r="AX3" s="211" t="s">
         <v>9</v>
       </c>
-      <c r="AY3" s="201" t="s">
+      <c r="AY3" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="AZ3" s="201"/>
-      <c r="BA3" s="195"/>
-      <c r="BB3" s="196"/>
-      <c r="BC3" s="194" t="s">
+      <c r="AZ3" s="200"/>
+      <c r="BA3" s="201"/>
+      <c r="BB3" s="202"/>
+      <c r="BC3" s="209" t="s">
         <v>14</v>
       </c>
-      <c r="BD3" s="201"/>
-      <c r="BE3" s="201"/>
-      <c r="BF3" s="195"/>
-      <c r="BG3" s="195"/>
-      <c r="BH3" s="196"/>
+      <c r="BD3" s="200"/>
+      <c r="BE3" s="200"/>
+      <c r="BF3" s="201"/>
+      <c r="BG3" s="201"/>
+      <c r="BH3" s="202"/>
       <c r="BI3" s="59"/>
-      <c r="BJ3" s="197" t="s">
+      <c r="BJ3" s="214" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="192" t="s">
+      <c r="BK3" s="211" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="198" t="s">
+      <c r="BL3" s="215" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="199"/>
-      <c r="BN3" s="200"/>
-      <c r="BO3" s="201" t="s">
+      <c r="BM3" s="216"/>
+      <c r="BN3" s="217"/>
+      <c r="BO3" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="195"/>
-      <c r="BQ3" s="195"/>
-      <c r="BR3" s="196"/>
+      <c r="BP3" s="201"/>
+      <c r="BQ3" s="201"/>
+      <c r="BR3" s="202"/>
       <c r="BS3" s="135"/>
     </row>
-    <row r="4" spans="1:71" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="203"/>
+    <row r="4" spans="1:73" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="185"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="191"/>
-      <c r="G4" s="191"/>
-      <c r="H4" s="191"/>
+      <c r="D4" s="204"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="204"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="204"/>
       <c r="I4" s="80" t="s">
         <v>3</v>
       </c>
@@ -7326,8 +7326,8 @@
         <v>24</v>
       </c>
       <c r="AB4" s="60"/>
-      <c r="AC4" s="193"/>
-      <c r="AD4" s="185"/>
+      <c r="AC4" s="212"/>
+      <c r="AD4" s="195"/>
       <c r="AE4" s="62" t="s">
         <v>27</v>
       </c>
@@ -7350,8 +7350,8 @@
         <v>24</v>
       </c>
       <c r="AL4" s="61"/>
-      <c r="AM4" s="184"/>
-      <c r="AN4" s="193"/>
+      <c r="AM4" s="194"/>
+      <c r="AN4" s="212"/>
       <c r="AO4" s="123" t="s">
         <v>27</v>
       </c>
@@ -7374,8 +7374,8 @@
         <v>24</v>
       </c>
       <c r="AV4" s="61"/>
-      <c r="AW4" s="193"/>
-      <c r="AX4" s="193"/>
+      <c r="AW4" s="212"/>
+      <c r="AX4" s="212"/>
       <c r="AY4" s="123" t="s">
         <v>27</v>
       </c>
@@ -7407,8 +7407,8 @@
         <v>24</v>
       </c>
       <c r="BI4" s="61"/>
-      <c r="BJ4" s="184"/>
-      <c r="BK4" s="193"/>
+      <c r="BJ4" s="194"/>
+      <c r="BK4" s="212"/>
       <c r="BL4" s="123" t="s">
         <v>32</v>
       </c>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="BS4" s="136"/>
     </row>
-    <row r="5" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="137"/>
       <c r="C5" s="138"/>
       <c r="D5" s="83"/>
@@ -7504,7 +7504,7 @@
       <c r="BR5" s="66"/>
       <c r="BS5" s="145"/>
     </row>
-    <row r="6" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="56">
         <v>46053</v>
       </c>
@@ -7740,8 +7740,9 @@
       <c r="BR6" s="157">
         <v>0.80972222222222223</v>
       </c>
+      <c r="BU6" s="175"/>
     </row>
-    <row r="7" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="166"/>
       <c r="B7" s="56">
         <f>B6+1</f>
@@ -7754,19 +7755,19 @@
       </c>
       <c r="E7" s="159">
         <f t="shared" ref="E7:E10" si="23">F7/D7</f>
-        <v>0.8114384748700173</v>
+        <v>0.78724436741767767</v>
       </c>
       <c r="F7" s="87">
         <f t="shared" ref="F7:F37" si="24">D7-H7</f>
-        <v>23410</v>
+        <v>22712</v>
       </c>
       <c r="G7" s="159">
         <f t="shared" ref="G7:G10" si="25">H7/D7</f>
-        <v>0.18856152512998267</v>
+        <v>0.21275563258232236</v>
       </c>
       <c r="H7" s="146">
         <f t="shared" ref="H7:H37" si="26">U7+AG7+AQ7+BB7</f>
-        <v>5440</v>
+        <v>6138</v>
       </c>
       <c r="I7" s="160">
         <f t="shared" ref="I7:I10" si="27">AE7/(AE7+AO7+BL7+AY7)</f>
@@ -7908,11 +7909,11 @@
       </c>
       <c r="AW7" s="110">
         <f t="shared" ref="AW7:AW10" si="42">BA7/AZ7</f>
-        <v>0.39726641272686536</v>
+        <v>0.24086937037866907</v>
       </c>
       <c r="AX7" s="110">
         <f t="shared" ref="AX7:AX10" si="43">BB7/AZ7</f>
-        <v>0.60273358727313464</v>
+        <v>0.75913062962133093</v>
       </c>
       <c r="AY7" s="111">
         <f t="shared" si="17"/>
@@ -7923,10 +7924,11 @@
       </c>
       <c r="BA7" s="120">
         <f t="shared" si="18"/>
-        <v>1773</v>
+        <v>1075</v>
       </c>
       <c r="BB7" s="113">
-        <v>2690</v>
+        <f>2690+698</f>
+        <v>3388</v>
       </c>
       <c r="BC7" s="112">
         <v>1520</v>
@@ -7981,7 +7983,7 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="8" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="166"/>
       <c r="B8" s="56">
         <f t="shared" ref="B8:B37" si="47">B7+1</f>
@@ -7994,19 +7996,19 @@
       </c>
       <c r="E8" s="159">
         <f t="shared" si="23"/>
-        <v>0.8527581641659312</v>
+        <v>0.83735657546337161</v>
       </c>
       <c r="F8" s="87">
         <f t="shared" si="24"/>
-        <v>38647</v>
+        <v>37949</v>
       </c>
       <c r="G8" s="159">
         <f t="shared" si="25"/>
-        <v>0.14724183583406886</v>
+        <v>0.16264342453662842</v>
       </c>
       <c r="H8" s="146">
         <f t="shared" si="26"/>
-        <v>6673</v>
+        <v>7371</v>
       </c>
       <c r="I8" s="160">
         <f t="shared" si="27"/>
@@ -8148,11 +8150,11 @@
       </c>
       <c r="AW8" s="110">
         <f t="shared" si="42"/>
-        <v>0.59245562130177509</v>
+        <v>0.48920118343195268</v>
       </c>
       <c r="AX8" s="110">
         <f t="shared" si="43"/>
-        <v>0.40754437869822485</v>
+        <v>0.51079881656804738</v>
       </c>
       <c r="AY8" s="111">
         <f t="shared" si="17"/>
@@ -8163,10 +8165,11 @@
       </c>
       <c r="BA8" s="120">
         <f t="shared" si="18"/>
-        <v>4005</v>
+        <v>3307</v>
       </c>
       <c r="BB8" s="113">
-        <v>2755</v>
+        <f>2755+698</f>
+        <v>3453</v>
       </c>
       <c r="BC8" s="112">
         <v>2724</v>
@@ -8221,7 +8224,7 @@
         <v>0.71805555555555556</v>
       </c>
     </row>
-    <row r="9" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="166" t="s">
         <v>67</v>
       </c>
@@ -8236,19 +8239,19 @@
       </c>
       <c r="E9" s="159">
         <f t="shared" si="23"/>
-        <v>0.85140475053193798</v>
+        <v>0.83624994572061317</v>
       </c>
       <c r="F9" s="87">
         <f t="shared" si="24"/>
-        <v>39214</v>
+        <v>38516</v>
       </c>
       <c r="G9" s="159">
         <f t="shared" si="25"/>
-        <v>0.14859524946806202</v>
+        <v>0.16375005427938685</v>
       </c>
       <c r="H9" s="146">
         <f t="shared" si="26"/>
-        <v>6844</v>
+        <v>7542</v>
       </c>
       <c r="I9" s="160">
         <f t="shared" si="27"/>
@@ -8390,11 +8393,11 @@
       </c>
       <c r="AW9" s="110">
         <f t="shared" si="42"/>
-        <v>0.64268401581834422</v>
+        <v>0.55364204617935964</v>
       </c>
       <c r="AX9" s="110">
         <f t="shared" si="43"/>
-        <v>0.35731598418165583</v>
+        <v>0.44635795382064036</v>
       </c>
       <c r="AY9" s="111">
         <f t="shared" si="17"/>
@@ -8405,10 +8408,11 @@
       </c>
       <c r="BA9" s="120">
         <f t="shared" si="18"/>
-        <v>5038</v>
+        <v>4340</v>
       </c>
       <c r="BB9" s="113">
-        <v>2801</v>
+        <f>2801+698</f>
+        <v>3499</v>
       </c>
       <c r="BC9" s="112">
         <v>3707</v>
@@ -8463,7 +8467,7 @@
         <v>0.58472222222222225</v>
       </c>
     </row>
-    <row r="10" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56">
         <f t="shared" si="47"/>
         <v>46057</v>
@@ -8475,19 +8479,19 @@
       </c>
       <c r="E10" s="159">
         <f t="shared" si="23"/>
-        <v>0.85418754175016698</v>
+        <v>0.83961673346693388</v>
       </c>
       <c r="F10" s="87">
         <f t="shared" si="24"/>
-        <v>40919</v>
+        <v>40221</v>
       </c>
       <c r="G10" s="159">
         <f t="shared" si="25"/>
-        <v>0.14581245824983299</v>
+        <v>0.16038326653306614</v>
       </c>
       <c r="H10" s="146">
         <f t="shared" si="26"/>
-        <v>6985</v>
+        <v>7683</v>
       </c>
       <c r="I10" s="160">
         <f t="shared" si="27"/>
@@ -8629,11 +8633,11 @@
       </c>
       <c r="AW10" s="110">
         <f t="shared" si="42"/>
-        <v>0.5880847433527655</v>
+        <v>0.48883833357031137</v>
       </c>
       <c r="AX10" s="110">
         <f t="shared" si="43"/>
-        <v>0.41191525664723444</v>
+        <v>0.51116166642968863</v>
       </c>
       <c r="AY10" s="111">
         <f t="shared" si="17"/>
@@ -8644,10 +8648,11 @@
       </c>
       <c r="BA10" s="120">
         <f t="shared" si="18"/>
-        <v>4136</v>
+        <v>3438</v>
       </c>
       <c r="BB10" s="113">
-        <v>2897</v>
+        <f>2897+698</f>
+        <v>3595</v>
       </c>
       <c r="BC10" s="112">
         <v>2932</v>
@@ -8705,7 +8710,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56">
         <f t="shared" si="47"/>
         <v>46058</v>
@@ -8717,19 +8722,19 @@
       </c>
       <c r="E11" s="159">
         <f t="shared" ref="E11:E24" si="52">F11/D11</f>
-        <v>0.84674657534246578</v>
+        <v>0.83180650684931512</v>
       </c>
       <c r="F11" s="87">
         <f t="shared" si="24"/>
-        <v>39560</v>
+        <v>38862</v>
       </c>
       <c r="G11" s="159">
         <f t="shared" ref="G11:G24" si="53">H11/D11</f>
-        <v>0.15325342465753425</v>
+        <v>0.16819349315068494</v>
       </c>
       <c r="H11" s="146">
         <f t="shared" si="26"/>
-        <v>7160</v>
+        <v>7858</v>
       </c>
       <c r="I11" s="160">
         <f t="shared" ref="I11:I24" si="54">AE11/(AE11+AO11+BL11+AY11)</f>
@@ -8871,11 +8876,11 @@
       </c>
       <c r="AW11" s="110">
         <f t="shared" ref="AW11:AW25" si="66">BA11/AZ11</f>
-        <v>0.57523645743766127</v>
+        <v>0.4752077959300659</v>
       </c>
       <c r="AX11" s="110">
         <f t="shared" ref="AX11:AX25" si="67">BB11/AZ11</f>
-        <v>0.42476354256233878</v>
+        <v>0.5247922040699341</v>
       </c>
       <c r="AY11" s="111">
         <f t="shared" si="17"/>
@@ -8886,10 +8891,11 @@
       </c>
       <c r="BA11" s="120">
         <f t="shared" si="18"/>
-        <v>4014</v>
+        <v>3316</v>
       </c>
       <c r="BB11" s="113">
-        <v>2964</v>
+        <f>2964+698</f>
+        <v>3662</v>
       </c>
       <c r="BC11" s="112">
         <v>2884</v>
@@ -8944,7 +8950,7 @@
         <v>0.84375</v>
       </c>
     </row>
-    <row r="12" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56">
         <f t="shared" si="47"/>
         <v>46059</v>
@@ -8956,19 +8962,19 @@
       </c>
       <c r="E12" s="159">
         <f t="shared" si="52"/>
-        <v>0.8465157243512631</v>
+        <v>0.83152173913043481</v>
       </c>
       <c r="F12" s="87">
         <f t="shared" si="24"/>
-        <v>39407</v>
+        <v>38709</v>
       </c>
       <c r="G12" s="159">
         <f>H12/D12</f>
-        <v>0.1534842756487369</v>
+        <v>0.16847826086956522</v>
       </c>
       <c r="H12" s="146">
         <f t="shared" si="26"/>
-        <v>7145</v>
+        <v>7843</v>
       </c>
       <c r="I12" s="160">
         <f t="shared" si="54"/>
@@ -9110,11 +9116,11 @@
       </c>
       <c r="AW12" s="110">
         <f t="shared" si="66"/>
-        <v>0.56714905933429816</v>
+        <v>0.46613603473227205</v>
       </c>
       <c r="AX12" s="110">
         <f t="shared" si="67"/>
-        <v>0.4328509406657019</v>
+        <v>0.53386396526772795</v>
       </c>
       <c r="AY12" s="111">
         <f t="shared" si="17"/>
@@ -9125,10 +9131,11 @@
       </c>
       <c r="BA12" s="120">
         <f t="shared" si="18"/>
-        <v>3919</v>
+        <v>3221</v>
       </c>
       <c r="BB12" s="113">
-        <v>2991</v>
+        <f>2991+698</f>
+        <v>3689</v>
       </c>
       <c r="BC12" s="112">
         <v>2715</v>
@@ -9183,7 +9190,7 @@
         <v>0.74305555555555558</v>
       </c>
     </row>
-    <row r="13" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56">
         <f t="shared" si="47"/>
         <v>46060</v>
@@ -9195,19 +9202,19 @@
       </c>
       <c r="E13" s="159">
         <f t="shared" si="52"/>
-        <v>0.82857142857142863</v>
+        <v>0.80801178203240054</v>
       </c>
       <c r="F13" s="87">
         <f t="shared" si="24"/>
-        <v>28130</v>
+        <v>27432</v>
       </c>
       <c r="G13" s="159">
         <f t="shared" si="53"/>
-        <v>0.17142857142857143</v>
+        <v>0.19198821796759941</v>
       </c>
       <c r="H13" s="146">
         <f t="shared" si="26"/>
-        <v>5820</v>
+        <v>6518</v>
       </c>
       <c r="I13" s="160">
         <f t="shared" si="54"/>
@@ -9349,11 +9356,11 @@
       </c>
       <c r="AW13" s="169">
         <f t="shared" si="66"/>
-        <v>0.43343343343343343</v>
+        <v>0.29369369369369369</v>
       </c>
       <c r="AX13" s="169">
         <f t="shared" si="67"/>
-        <v>0.56656656656656657</v>
+        <v>0.70630630630630631</v>
       </c>
       <c r="AY13" s="111">
         <f t="shared" si="17"/>
@@ -9364,10 +9371,11 @@
       </c>
       <c r="BA13" s="120">
         <f t="shared" si="18"/>
-        <v>2165</v>
+        <v>1467</v>
       </c>
       <c r="BB13" s="113">
-        <v>2830</v>
+        <f>2830+698</f>
+        <v>3528</v>
       </c>
       <c r="BC13" s="112">
         <v>1598</v>
@@ -9422,7 +9430,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56">
         <f t="shared" si="47"/>
         <v>46061</v>
@@ -9434,19 +9442,19 @@
       </c>
       <c r="E14" s="159">
         <f t="shared" si="52"/>
-        <v>0.78541281007034436</v>
+        <v>0.75957052943354308</v>
       </c>
       <c r="F14" s="87">
         <f t="shared" si="24"/>
-        <v>21214</v>
+        <v>20516</v>
       </c>
       <c r="G14" s="159">
         <f t="shared" si="53"/>
-        <v>0.21458718992965567</v>
+        <v>0.24042947056645686</v>
       </c>
       <c r="H14" s="146">
         <f t="shared" si="26"/>
-        <v>5796</v>
+        <v>6494</v>
       </c>
       <c r="I14" s="160">
         <f t="shared" si="54"/>
@@ -9588,11 +9596,11 @@
       </c>
       <c r="AW14" s="110">
         <f t="shared" si="66"/>
-        <v>0.38591983556012333</v>
+        <v>0.2065775950668037</v>
       </c>
       <c r="AX14" s="110">
         <f t="shared" si="67"/>
-        <v>0.61408016443987667</v>
+        <v>0.79342240493319627</v>
       </c>
       <c r="AY14" s="111">
         <f t="shared" si="17"/>
@@ -9603,10 +9611,11 @@
       </c>
       <c r="BA14" s="120">
         <f t="shared" si="18"/>
-        <v>1502</v>
+        <v>804</v>
       </c>
       <c r="BB14" s="113">
-        <v>2390</v>
+        <f>2390+698</f>
+        <v>3088</v>
       </c>
       <c r="BC14" s="112">
         <v>1495</v>
@@ -9661,7 +9670,7 @@
         <v>0.41736111111111113</v>
       </c>
     </row>
-    <row r="15" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="56">
         <f t="shared" si="47"/>
         <v>46062</v>
@@ -9673,19 +9682,19 @@
       </c>
       <c r="E15" s="159">
         <f t="shared" si="52"/>
-        <v>0.85265700483091789</v>
+        <v>0.83732981993851563</v>
       </c>
       <c r="F15" s="87">
         <f t="shared" si="24"/>
-        <v>38830</v>
+        <v>38132</v>
       </c>
       <c r="G15" s="159">
         <f t="shared" si="53"/>
-        <v>0.14734299516908211</v>
+        <v>0.1626701800614844</v>
       </c>
       <c r="H15" s="146">
         <f t="shared" si="26"/>
-        <v>6710</v>
+        <v>7408</v>
       </c>
       <c r="I15" s="160">
         <f t="shared" si="54"/>
@@ -9827,11 +9836,11 @@
       </c>
       <c r="AW15" s="169">
         <f t="shared" si="66"/>
-        <v>0.5865102639296188</v>
+        <v>0.48416422287390032</v>
       </c>
       <c r="AX15" s="169">
         <f t="shared" si="67"/>
-        <v>0.41348973607038125</v>
+        <v>0.51583577712609974</v>
       </c>
       <c r="AY15" s="111">
         <f t="shared" si="17"/>
@@ -9842,10 +9851,11 @@
       </c>
       <c r="BA15" s="120">
         <f t="shared" si="18"/>
-        <v>4000</v>
+        <v>3302</v>
       </c>
       <c r="BB15" s="113">
-        <v>2820</v>
+        <f>2820+698</f>
+        <v>3518</v>
       </c>
       <c r="BC15" s="112">
         <v>2790</v>
@@ -9900,7 +9910,7 @@
         <v>0.72916666666666663</v>
       </c>
     </row>
-    <row r="16" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="56">
         <f t="shared" si="47"/>
         <v>46063</v>
@@ -9912,19 +9922,19 @@
       </c>
       <c r="E16" s="159">
         <f t="shared" si="52"/>
-        <v>0.84562120812450536</v>
+        <v>0.83027785105073415</v>
       </c>
       <c r="F16" s="87">
         <f t="shared" si="24"/>
-        <v>38469</v>
+        <v>37771</v>
       </c>
       <c r="G16" s="159">
         <f t="shared" si="53"/>
-        <v>0.15437879187549458</v>
+        <v>0.16972214894926579</v>
       </c>
       <c r="H16" s="146">
         <f t="shared" si="26"/>
-        <v>7023</v>
+        <v>7721</v>
       </c>
       <c r="I16" s="160">
         <f t="shared" si="54"/>
@@ -10066,11 +10076,11 @@
       </c>
       <c r="AW16" s="110">
         <f t="shared" si="66"/>
-        <v>0.56834427425237055</v>
+        <v>0.46652078774617067</v>
       </c>
       <c r="AX16" s="110">
         <f t="shared" si="67"/>
-        <v>0.43165572574762945</v>
+        <v>0.53347921225382933</v>
       </c>
       <c r="AY16" s="111">
         <f t="shared" si="17"/>
@@ -10081,10 +10091,11 @@
       </c>
       <c r="BA16" s="120">
         <f t="shared" si="18"/>
-        <v>3896</v>
+        <v>3198</v>
       </c>
       <c r="BB16" s="113">
-        <v>2959</v>
+        <f>2959+698</f>
+        <v>3657</v>
       </c>
       <c r="BC16" s="112">
         <v>2813</v>
@@ -10151,19 +10162,19 @@
       </c>
       <c r="E17" s="159">
         <f t="shared" si="52"/>
-        <v>0.84606986899563319</v>
+        <v>0.83082969432314413</v>
       </c>
       <c r="F17" s="87">
         <f t="shared" si="24"/>
-        <v>38750</v>
+        <v>38052</v>
       </c>
       <c r="G17" s="159">
         <f t="shared" si="53"/>
-        <v>0.15393013100436681</v>
+        <v>0.1691703056768559</v>
       </c>
       <c r="H17" s="146">
         <f t="shared" si="26"/>
-        <v>7050</v>
+        <v>7748</v>
       </c>
       <c r="I17" s="160">
         <f t="shared" si="54"/>
@@ -10305,11 +10316,11 @@
       </c>
       <c r="AW17" s="110">
         <f t="shared" si="66"/>
-        <v>0.57184325108853407</v>
+        <v>0.47053701015965166</v>
       </c>
       <c r="AX17" s="110">
         <f t="shared" si="67"/>
-        <v>0.42815674891146588</v>
+        <v>0.52946298984034834</v>
       </c>
       <c r="AY17" s="111">
         <f t="shared" si="17"/>
@@ -10320,10 +10331,11 @@
       </c>
       <c r="BA17" s="120">
         <f t="shared" si="18"/>
-        <v>3940</v>
+        <v>3242</v>
       </c>
       <c r="BB17" s="113">
-        <v>2950</v>
+        <f>2950+698</f>
+        <v>3648</v>
       </c>
       <c r="BC17" s="112">
         <v>2830</v>
@@ -10390,19 +10402,19 @@
       </c>
       <c r="E18" s="159">
         <f t="shared" si="52"/>
-        <v>0.84980037536256614</v>
+        <v>0.83491383722914181</v>
       </c>
       <c r="F18" s="87">
         <f t="shared" si="24"/>
-        <v>39845.440000000002</v>
+        <v>39147.440000000002</v>
       </c>
       <c r="G18" s="159">
         <f t="shared" si="53"/>
-        <v>0.15019962463743389</v>
+        <v>0.16508616277085819</v>
       </c>
       <c r="H18" s="146">
         <f t="shared" si="26"/>
-        <v>7042.5599999999995</v>
+        <v>7740.5599999999995</v>
       </c>
       <c r="I18" s="160">
         <f t="shared" si="54"/>
@@ -10544,11 +10556,11 @@
       </c>
       <c r="AW18" s="110">
         <f t="shared" si="66"/>
-        <v>0.56763152213026269</v>
+        <v>0.46716372795969774</v>
       </c>
       <c r="AX18" s="110">
         <f t="shared" si="67"/>
-        <v>0.43236847786973731</v>
+        <v>0.53283627204030226</v>
       </c>
       <c r="AY18" s="111">
         <f t="shared" si="17"/>
@@ -10559,10 +10571,11 @@
       </c>
       <c r="BA18" s="120">
         <f t="shared" si="18"/>
-        <v>3943.62</v>
+        <v>3245.62</v>
       </c>
       <c r="BB18" s="113">
-        <v>3003.88</v>
+        <f>3003.88+698</f>
+        <v>3701.88</v>
       </c>
       <c r="BC18" s="112">
         <v>2596.62</v>
@@ -10629,19 +10642,19 @@
       </c>
       <c r="E19" s="159">
         <f t="shared" si="52"/>
-        <v>0.84242516665940481</v>
+        <v>0.82721885756611913</v>
       </c>
       <c r="F19" s="87">
         <f t="shared" si="24"/>
-        <v>38669</v>
+        <v>37971</v>
       </c>
       <c r="G19" s="159">
         <f t="shared" si="53"/>
-        <v>0.15757483334059519</v>
+        <v>0.17278114243388087</v>
       </c>
       <c r="H19" s="146">
         <f t="shared" si="26"/>
-        <v>7233</v>
+        <v>7931</v>
       </c>
       <c r="I19" s="160">
         <f t="shared" si="54"/>
@@ -10783,11 +10796,11 @@
       </c>
       <c r="AW19" s="110">
         <f t="shared" ref="AW19" si="75">BA19/AZ19</f>
-        <v>0.55771151376801253</v>
+        <v>0.45812526751319732</v>
       </c>
       <c r="AX19" s="110">
         <f t="shared" ref="AX19" si="76">BB19/AZ19</f>
-        <v>0.44228848623198747</v>
+        <v>0.54187473248680273</v>
       </c>
       <c r="AY19" s="111">
         <f t="shared" si="17"/>
@@ -10798,10 +10811,11 @@
       </c>
       <c r="BA19" s="120">
         <f t="shared" si="18"/>
-        <v>3909</v>
+        <v>3211</v>
       </c>
       <c r="BB19" s="113">
-        <v>3100</v>
+        <f>3100+698</f>
+        <v>3798</v>
       </c>
       <c r="BC19" s="182">
         <v>2555</v>
@@ -10868,19 +10882,19 @@
       </c>
       <c r="E20" s="159">
         <f t="shared" si="52"/>
-        <v>0.8076687975646879</v>
+        <v>0.786420700152207</v>
       </c>
       <c r="F20" s="87">
         <f t="shared" si="24"/>
-        <v>26531.919999999998</v>
+        <v>25833.919999999998</v>
       </c>
       <c r="G20" s="159">
         <f t="shared" si="53"/>
-        <v>0.19233120243531202</v>
+        <v>0.213579299847793</v>
       </c>
       <c r="H20" s="146">
         <f t="shared" si="26"/>
-        <v>6318.08</v>
+        <v>7016.08</v>
       </c>
       <c r="I20" s="160">
         <f t="shared" si="54"/>
@@ -11022,11 +11036,11 @@
       </c>
       <c r="AW20" s="110">
         <f t="shared" si="66"/>
-        <v>0.41872099020113462</v>
+        <v>0.27472924187725634</v>
       </c>
       <c r="AX20" s="110">
         <f t="shared" si="67"/>
-        <v>0.58127900979886538</v>
+        <v>0.72527075812274366</v>
       </c>
       <c r="AY20" s="111">
         <f t="shared" si="17"/>
@@ -11037,10 +11051,11 @@
       </c>
       <c r="BA20" s="120">
         <f t="shared" si="18"/>
-        <v>2029.75</v>
+        <v>1331.75</v>
       </c>
       <c r="BB20" s="113">
-        <v>2817.75</v>
+        <f>2817.75+698</f>
+        <v>3515.75</v>
       </c>
       <c r="BC20" s="112">
         <v>1946.53</v>
@@ -11108,19 +11123,19 @@
       </c>
       <c r="E21" s="159">
         <f t="shared" si="52"/>
-        <v>0.77950310559006208</v>
+        <v>0.75644244746927447</v>
       </c>
       <c r="F21" s="87">
         <f t="shared" si="24"/>
-        <v>23594</v>
+        <v>22896</v>
       </c>
       <c r="G21" s="159">
         <f t="shared" si="53"/>
-        <v>0.22049689440993789</v>
+        <v>0.24355755253072553</v>
       </c>
       <c r="H21" s="146">
         <f t="shared" si="26"/>
-        <v>6674</v>
+        <v>7372</v>
       </c>
       <c r="I21" s="160">
         <f t="shared" si="54"/>
@@ -11262,11 +11277,11 @@
       </c>
       <c r="AW21" s="110">
         <f t="shared" si="66"/>
-        <v>0.40219416269923414</v>
+        <v>0.25771061891947838</v>
       </c>
       <c r="AX21" s="110">
         <f t="shared" si="67"/>
-        <v>0.59780583730076586</v>
+        <v>0.74228938108052167</v>
       </c>
       <c r="AY21" s="111">
         <f t="shared" si="17"/>
@@ -11277,10 +11292,11 @@
       </c>
       <c r="BA21" s="120">
         <f t="shared" si="18"/>
-        <v>1943</v>
+        <v>1245</v>
       </c>
       <c r="BB21" s="113">
-        <v>2888</v>
+        <f>2888+698</f>
+        <v>3586</v>
       </c>
       <c r="BC21" s="112">
         <v>2290</v>
@@ -11348,19 +11364,19 @@
       </c>
       <c r="E22" s="159">
         <f t="shared" si="52"/>
-        <v>0.8443995643097032</v>
+        <v>0.82856040664427699</v>
       </c>
       <c r="F22" s="87">
         <f t="shared" si="24"/>
-        <v>37211</v>
+        <v>36513</v>
       </c>
       <c r="G22" s="159">
         <f t="shared" si="53"/>
-        <v>0.1556004356902968</v>
+        <v>0.17143959335572298</v>
       </c>
       <c r="H22" s="146">
         <f t="shared" si="26"/>
-        <v>6857</v>
+        <v>7555</v>
       </c>
       <c r="I22" s="160">
         <f t="shared" si="54"/>
@@ -11502,11 +11518,11 @@
       </c>
       <c r="AW22" s="110">
         <f t="shared" si="66"/>
-        <v>0.55276763990267641</v>
+        <v>0.44662408759124089</v>
       </c>
       <c r="AX22" s="110">
         <f t="shared" si="67"/>
-        <v>0.44723236009732359</v>
+        <v>0.55337591240875916</v>
       </c>
       <c r="AY22" s="111">
         <f t="shared" si="17"/>
@@ -11517,10 +11533,11 @@
       </c>
       <c r="BA22" s="120">
         <f t="shared" si="18"/>
-        <v>3635</v>
+        <v>2937</v>
       </c>
       <c r="BB22" s="113">
-        <v>2941</v>
+        <f>2941+698</f>
+        <v>3639</v>
       </c>
       <c r="BC22" s="112">
         <v>2799</v>
@@ -11588,19 +11605,19 @@
       </c>
       <c r="E23" s="159">
         <f t="shared" si="52"/>
-        <v>0.85246835700622681</v>
+        <v>0.83826462089455045</v>
       </c>
       <c r="F23" s="87">
         <f t="shared" si="24"/>
-        <v>41892</v>
+        <v>41194</v>
       </c>
       <c r="G23" s="159">
         <f t="shared" si="53"/>
-        <v>0.14753164299377314</v>
+        <v>0.16173537910544952</v>
       </c>
       <c r="H23" s="146">
         <f t="shared" si="26"/>
-        <v>7250</v>
+        <v>7948</v>
       </c>
       <c r="I23" s="160">
         <f t="shared" si="54"/>
@@ -11742,11 +11759,11 @@
       </c>
       <c r="AW23" s="110">
         <f t="shared" si="66"/>
-        <v>0.5708430113403471</v>
+        <v>0.47547479163820194</v>
       </c>
       <c r="AX23" s="110">
         <f t="shared" si="67"/>
-        <v>0.42915698865965296</v>
+        <v>0.52452520836179806</v>
       </c>
       <c r="AY23" s="111">
         <f t="shared" si="17"/>
@@ -11757,10 +11774,11 @@
       </c>
       <c r="BA23" s="120">
         <f t="shared" si="18"/>
-        <v>4178</v>
+        <v>3480</v>
       </c>
       <c r="BB23" s="113">
-        <v>3141</v>
+        <f>3141+698</f>
+        <v>3839</v>
       </c>
       <c r="BC23" s="112">
         <v>3016</v>
@@ -11828,19 +11846,19 @@
       </c>
       <c r="E24" s="159">
         <f t="shared" si="52"/>
-        <v>0.86412639405204461</v>
+        <v>0.85115241635687733</v>
       </c>
       <c r="F24" s="87">
         <f t="shared" si="24"/>
-        <v>46490</v>
+        <v>45792</v>
       </c>
       <c r="G24" s="159">
         <f t="shared" si="53"/>
-        <v>0.13587360594795539</v>
+        <v>0.14884758364312267</v>
       </c>
       <c r="H24" s="146">
         <f t="shared" si="26"/>
-        <v>7310</v>
+        <v>8008</v>
       </c>
       <c r="I24" s="160">
         <f t="shared" si="54"/>
@@ -11982,11 +12000,11 @@
       </c>
       <c r="AW24" s="110">
         <f t="shared" si="66"/>
-        <v>0.57774798927613946</v>
+        <v>0.48418230563002679</v>
       </c>
       <c r="AX24" s="110">
         <f t="shared" si="67"/>
-        <v>0.42225201072386059</v>
+        <v>0.51581769436997316</v>
       </c>
       <c r="AY24" s="111">
         <f t="shared" si="17"/>
@@ -11997,10 +12015,11 @@
       </c>
       <c r="BA24" s="120">
         <f t="shared" si="18"/>
-        <v>4310</v>
+        <v>3612</v>
       </c>
       <c r="BB24" s="113">
-        <v>3150</v>
+        <f>3150+698</f>
+        <v>3848</v>
       </c>
       <c r="BC24" s="112">
         <v>3105</v>
@@ -12068,19 +12087,19 @@
       </c>
       <c r="E25" s="159">
         <f t="shared" ref="E25:E36" si="80">F25/D25</f>
-        <v>0.86429861992080881</v>
+        <v>0.85088225118210126</v>
       </c>
       <c r="F25" s="87">
         <f t="shared" si="24"/>
-        <v>44966</v>
+        <v>44268</v>
       </c>
       <c r="G25" s="159">
         <f t="shared" ref="G25:G36" si="81">H25/D25</f>
-        <v>0.13570138007919116</v>
+        <v>0.14911774881789874</v>
       </c>
       <c r="H25" s="146">
         <f t="shared" si="26"/>
-        <v>7060</v>
+        <v>7758</v>
       </c>
       <c r="I25" s="160">
         <f t="shared" ref="I25:I36" si="82">AE25/(AE25+AO25+BL25+AY25)</f>
@@ -12222,11 +12241,11 @@
       </c>
       <c r="AW25" s="169">
         <f t="shared" si="66"/>
-        <v>0.59754344701424278</v>
+        <v>0.50633738403240558</v>
       </c>
       <c r="AX25" s="169">
         <f t="shared" si="67"/>
-        <v>0.40245655298575722</v>
+        <v>0.49366261596759442</v>
       </c>
       <c r="AY25" s="111">
         <f t="shared" si="17"/>
@@ -12237,10 +12256,11 @@
       </c>
       <c r="BA25" s="120">
         <f t="shared" si="18"/>
-        <v>4573</v>
+        <v>3875</v>
       </c>
       <c r="BB25" s="113">
-        <v>3080</v>
+        <f>3080+698</f>
+        <v>3778</v>
       </c>
       <c r="BC25" s="112">
         <v>4183</v>
@@ -12308,19 +12328,19 @@
       </c>
       <c r="E26" s="159">
         <f t="shared" si="80"/>
-        <v>0.85937180901033372</v>
+        <v>0.84511701997304256</v>
       </c>
       <c r="F26" s="87">
         <f t="shared" si="24"/>
-        <v>42080</v>
+        <v>41382</v>
       </c>
       <c r="G26" s="159">
         <f t="shared" si="81"/>
-        <v>0.14062819098966631</v>
+        <v>0.15488298002695747</v>
       </c>
       <c r="H26" s="146">
         <f t="shared" si="26"/>
-        <v>6886</v>
+        <v>7584</v>
       </c>
       <c r="I26" s="160">
         <f t="shared" si="82"/>
@@ -12462,11 +12482,11 @@
       </c>
       <c r="AW26" s="110">
         <f t="shared" ref="AW26:AW36" si="94">BA26/AZ26</f>
-        <v>0.57327899869014698</v>
+        <v>0.47169262116140298</v>
       </c>
       <c r="AX26" s="110">
         <f t="shared" ref="AX26:AX36" si="95">BB26/AZ26</f>
-        <v>0.42672100130985302</v>
+        <v>0.52830737883859702</v>
       </c>
       <c r="AY26" s="111">
         <f t="shared" si="17"/>
@@ -12477,10 +12497,11 @@
       </c>
       <c r="BA26" s="120">
         <f t="shared" si="18"/>
-        <v>3939</v>
+        <v>3241</v>
       </c>
       <c r="BB26" s="113">
-        <v>2932</v>
+        <f>2932+698</f>
+        <v>3630</v>
       </c>
       <c r="BC26" s="112">
         <v>2940</v>
@@ -12548,19 +12569,19 @@
       </c>
       <c r="E27" s="159">
         <f t="shared" si="80"/>
-        <v>0.80312370339636063</v>
+        <v>0.78243731847549047</v>
       </c>
       <c r="F27" s="87">
         <f t="shared" si="24"/>
-        <v>27099</v>
+        <v>26401</v>
       </c>
       <c r="G27" s="159">
         <f t="shared" si="81"/>
-        <v>0.19687629660363939</v>
+        <v>0.21756268152450953</v>
       </c>
       <c r="H27" s="146">
         <f t="shared" si="26"/>
-        <v>6643</v>
+        <v>7341</v>
       </c>
       <c r="I27" s="160">
         <f t="shared" si="82"/>
@@ -12702,11 +12723,11 @@
       </c>
       <c r="AW27" s="110">
         <f t="shared" si="94"/>
-        <v>0.42192222446101146</v>
+        <v>0.28128148297400768</v>
       </c>
       <c r="AX27" s="110">
         <f t="shared" si="95"/>
-        <v>0.57807777553898854</v>
+        <v>0.71871851702599232</v>
       </c>
       <c r="AY27" s="111">
         <f t="shared" si="17"/>
@@ -12717,10 +12738,11 @@
       </c>
       <c r="BA27" s="120">
         <f t="shared" si="18"/>
-        <v>2094</v>
+        <v>1396</v>
       </c>
       <c r="BB27" s="113">
-        <v>2869</v>
+        <f>2869+698</f>
+        <v>3567</v>
       </c>
       <c r="BC27" s="112">
         <v>1596</v>
@@ -13028,19 +13050,19 @@
       </c>
       <c r="E29" s="159">
         <f t="shared" si="80"/>
-        <v>0.84299087247171756</v>
+        <v>0.84026975488515598</v>
       </c>
       <c r="F29" s="87">
         <f t="shared" si="24"/>
-        <v>39344.07</v>
+        <v>39217.07</v>
       </c>
       <c r="G29" s="159">
         <f t="shared" si="81"/>
-        <v>0.1570091275282825</v>
+        <v>0.15973024511484402</v>
       </c>
       <c r="H29" s="146">
         <f t="shared" si="26"/>
-        <v>7327.93</v>
+        <v>7454.93</v>
       </c>
       <c r="I29" s="160">
         <f t="shared" si="82"/>
@@ -13182,11 +13204,11 @@
       </c>
       <c r="AW29" s="110">
         <f t="shared" si="94"/>
-        <v>0.49066060244557114</v>
+        <v>0.47172233820459286</v>
       </c>
       <c r="AX29" s="110">
         <f t="shared" si="95"/>
-        <v>0.50933939755442892</v>
+        <v>0.52827766179540714</v>
       </c>
       <c r="AY29" s="111">
         <f t="shared" si="17"/>
@@ -13197,11 +13219,11 @@
       </c>
       <c r="BA29" s="120">
         <f t="shared" si="18"/>
-        <v>3290.37</v>
+        <v>3163.37</v>
       </c>
       <c r="BB29" s="181">
         <f>2844.63+BB40</f>
-        <v>3415.63</v>
+        <v>3542.63</v>
       </c>
       <c r="BC29" s="112">
         <v>2793.52</v>
@@ -13269,19 +13291,19 @@
       </c>
       <c r="E30" s="159">
         <f t="shared" si="80"/>
-        <v>0.84268299995716789</v>
+        <v>0.83996316443226104</v>
       </c>
       <c r="F30" s="87">
         <f t="shared" si="24"/>
-        <v>39348.239999999998</v>
+        <v>39221.24</v>
       </c>
       <c r="G30" s="159">
         <f t="shared" si="81"/>
-        <v>0.15731700004283206</v>
+        <v>0.1600368355677389</v>
       </c>
       <c r="H30" s="146">
         <f t="shared" si="26"/>
-        <v>7345.76</v>
+        <v>7472.76</v>
       </c>
       <c r="I30" s="160">
         <f t="shared" si="82"/>
@@ -13423,11 +13445,11 @@
       </c>
       <c r="AW30" s="110">
         <f t="shared" si="94"/>
-        <v>0.50407331975560077</v>
+        <v>0.48559790514983997</v>
       </c>
       <c r="AX30" s="110">
         <f t="shared" si="95"/>
-        <v>0.49592668024439918</v>
+        <v>0.51440209485015997</v>
       </c>
       <c r="AY30" s="111">
         <f t="shared" si="17"/>
@@ -13438,11 +13460,11 @@
       </c>
       <c r="BA30" s="120">
         <f t="shared" si="18"/>
-        <v>3465</v>
+        <v>3338</v>
       </c>
       <c r="BB30" s="113">
         <f>2838+BB40</f>
-        <v>3409</v>
+        <v>3536</v>
       </c>
       <c r="BC30" s="112">
         <v>2737.25</v>
@@ -13510,19 +13532,19 @@
       </c>
       <c r="E31" s="159">
         <f t="shared" si="80"/>
-        <v>0.83914088314809254</v>
+        <v>0.83641591211432009</v>
       </c>
       <c r="F31" s="87">
         <f t="shared" si="24"/>
-        <v>39109</v>
+        <v>38982</v>
       </c>
       <c r="G31" s="159">
         <f t="shared" si="81"/>
-        <v>0.16085911685190749</v>
+        <v>0.16358408788567996</v>
       </c>
       <c r="H31" s="146">
         <f t="shared" si="26"/>
-        <v>7497</v>
+        <v>7624</v>
       </c>
       <c r="I31" s="160">
         <f t="shared" si="82"/>
@@ -13664,11 +13686,11 @@
       </c>
       <c r="AW31" s="110">
         <f t="shared" si="94"/>
-        <v>0.54964856230031944</v>
+        <v>0.53341853035143771</v>
       </c>
       <c r="AX31" s="110">
         <f t="shared" si="95"/>
-        <v>0.4503514376996805</v>
+        <v>0.46658146964856229</v>
       </c>
       <c r="AY31" s="111">
         <f t="shared" si="17"/>
@@ -13679,11 +13701,11 @@
       </c>
       <c r="BA31" s="120">
         <f t="shared" si="18"/>
-        <v>4301</v>
+        <v>4174</v>
       </c>
       <c r="BB31" s="113">
         <f>2953+BB40</f>
-        <v>3524</v>
+        <v>3651</v>
       </c>
       <c r="BC31" s="112">
         <v>3651</v>
@@ -13751,19 +13773,19 @@
       </c>
       <c r="E32" s="159">
         <f t="shared" si="80"/>
-        <v>0.83382352941176474</v>
+        <v>0.83103599648814752</v>
       </c>
       <c r="F32" s="87">
         <f t="shared" si="24"/>
-        <v>37989</v>
+        <v>37862</v>
       </c>
       <c r="G32" s="159">
         <f t="shared" si="81"/>
-        <v>0.16617647058823529</v>
+        <v>0.16896400351185251</v>
       </c>
       <c r="H32" s="146">
         <f t="shared" si="26"/>
-        <v>7571</v>
+        <v>7698</v>
       </c>
       <c r="I32" s="160">
         <f t="shared" si="82"/>
@@ -13905,11 +13927,11 @@
       </c>
       <c r="AW32" s="169">
         <f t="shared" si="94"/>
-        <v>0.50537190082644623</v>
+        <v>0.48787878787878786</v>
       </c>
       <c r="AX32" s="169">
         <f t="shared" si="95"/>
-        <v>0.49462809917355371</v>
+        <v>0.51212121212121209</v>
       </c>
       <c r="AY32" s="111">
         <f t="shared" si="17"/>
@@ -13920,11 +13942,11 @@
       </c>
       <c r="BA32" s="120">
         <f t="shared" si="18"/>
-        <v>3669</v>
+        <v>3542</v>
       </c>
       <c r="BB32" s="113">
         <f>3020+BB40</f>
-        <v>3591</v>
+        <v>3718</v>
       </c>
       <c r="BC32" s="112">
         <v>2780</v>
@@ -13992,19 +14014,19 @@
       </c>
       <c r="E33" s="159">
         <f t="shared" si="80"/>
-        <v>0.84566036173999426</v>
+        <v>0.84303215926493114</v>
       </c>
       <c r="F33" s="87">
         <f t="shared" si="24"/>
-        <v>40864</v>
+        <v>40737</v>
       </c>
       <c r="G33" s="159">
         <f t="shared" si="81"/>
-        <v>0.1543396382600058</v>
+        <v>0.15696784073506892</v>
       </c>
       <c r="H33" s="146">
         <f t="shared" si="26"/>
-        <v>7458</v>
+        <v>7585</v>
       </c>
       <c r="I33" s="160">
         <f t="shared" si="82"/>
@@ -14145,11 +14167,11 @@
       </c>
       <c r="AW33" s="169">
         <f t="shared" si="94"/>
-        <v>0.47558985012613147</v>
+        <v>0.45674432408369192</v>
       </c>
       <c r="AX33" s="169">
         <f t="shared" si="95"/>
-        <v>0.52441014987386858</v>
+        <v>0.54325567591630808</v>
       </c>
       <c r="AY33" s="111">
         <f t="shared" si="17"/>
@@ -14160,11 +14182,11 @@
       </c>
       <c r="BA33" s="120">
         <f t="shared" si="18"/>
-        <v>3205</v>
+        <v>3078</v>
       </c>
       <c r="BB33" s="113">
         <f>2963+BB40</f>
-        <v>3534</v>
+        <v>3661</v>
       </c>
       <c r="BC33" s="112">
         <v>3131</v>
@@ -14232,19 +14254,19 @@
       </c>
       <c r="E34" s="159">
         <f t="shared" si="80"/>
-        <v>0.79766709049698714</v>
+        <v>0.79415666979932553</v>
       </c>
       <c r="F34" s="87">
         <f t="shared" si="24"/>
-        <v>28858</v>
+        <v>28731</v>
       </c>
       <c r="G34" s="159">
         <f t="shared" si="81"/>
-        <v>0.20233290950301289</v>
+        <v>0.20584333020067444</v>
       </c>
       <c r="H34" s="146">
-        <f t="shared" si="26"/>
-        <v>7320</v>
+        <f>U34+AG34+AQ34+BB34</f>
+        <v>7447</v>
       </c>
       <c r="I34" s="160">
         <f t="shared" si="82"/>
@@ -14386,11 +14408,11 @@
       </c>
       <c r="AW34" s="110">
         <f t="shared" si="94"/>
-        <v>0.31655092592592593</v>
+        <v>0.29205246913580246</v>
       </c>
       <c r="AX34" s="110">
         <f t="shared" si="95"/>
-        <v>0.68344907407407407</v>
+        <v>0.70794753086419748</v>
       </c>
       <c r="AY34" s="111">
         <f t="shared" si="17"/>
@@ -14401,11 +14423,11 @@
       </c>
       <c r="BA34" s="120">
         <f t="shared" si="18"/>
-        <v>1641</v>
+        <v>1514</v>
       </c>
       <c r="BB34" s="113">
         <f>2972+BB40</f>
-        <v>3543</v>
+        <v>3670</v>
       </c>
       <c r="BC34" s="112">
         <v>1604</v>
@@ -14975,7 +14997,7 @@
     </row>
     <row r="40" spans="1:70" x14ac:dyDescent="0.25">
       <c r="BB40" s="52">
-        <v>571</v>
+        <v>698</v>
       </c>
     </row>
     <row r="41" spans="1:70" x14ac:dyDescent="0.25">
@@ -14984,6 +15006,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BJ1:BR2"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="AR3:AU3"/>
+    <mergeCell ref="BJ3:BJ4"/>
+    <mergeCell ref="BK3:BK4"/>
+    <mergeCell ref="BL3:BN3"/>
+    <mergeCell ref="BO3:BR3"/>
+    <mergeCell ref="AW1:BH2"/>
+    <mergeCell ref="AW3:AW4"/>
+    <mergeCell ref="AX3:AX4"/>
+    <mergeCell ref="AY3:BB3"/>
+    <mergeCell ref="BC3:BH3"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="D1:P2"/>
     <mergeCell ref="R1:AA2"/>
@@ -15000,22 +15038,6 @@
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="AH3:AK3"/>
     <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="BJ1:BR2"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="AR3:AU3"/>
-    <mergeCell ref="BJ3:BJ4"/>
-    <mergeCell ref="BK3:BK4"/>
-    <mergeCell ref="BL3:BN3"/>
-    <mergeCell ref="BO3:BR3"/>
-    <mergeCell ref="AW1:BH2"/>
-    <mergeCell ref="AW3:AW4"/>
-    <mergeCell ref="AX3:AX4"/>
-    <mergeCell ref="AY3:BB3"/>
-    <mergeCell ref="BC3:BH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -19050,6 +19072,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <SharedWithUsers xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -19296,43 +19347,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <SharedWithUsers xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9276BEC0-A699-496F-9D0D-FC21BE20BC34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B2FF829-496F-411A-A9F9-F094E298C353}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{595F6CD4-808F-449C-9B9B-391474399047}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{595F6CD4-808F-449C-9B9B-391474399047}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B2FF829-496F-411A-A9F9-F094E298C353}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9276BEC0-A699-496F-9D0D-FC21BE20BC34}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>